--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260831.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>608,790,000</t>
+          <t>610,250,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.33%</t>
+          <t>15.11%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>682,540,000</t>
+          <t>683,490,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.59%</t>
+          <t>12.99%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>179,200,000</t>
+          <t>179,240,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.42%</t>
+          <t>10.43%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>10.28%</t>
+          <t>10.16%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,231,040,000</t>
+          <t>1,231,580,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>8.07%</t>
+          <t>8.16%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>36,770,000</t>
+          <t>36,780,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>6.20%</t>
+          <t>6.32%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.87%</t>
+          <t>4.95%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.97%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>127,400,000</t>
+          <t>127,450,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>91,870,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>91,450,000</t>
+          <t>484</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1056,51 +1056,51 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>119,300,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>119,300,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1210,46 +1210,46 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>29,940,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>29,940,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1320,24 +1320,24 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>8,010,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,22 +1371,22 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>8,010,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>3,019,307,514</t>
+          <t>3,186,572,724</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,233,227,576</t>
+          <t>1,195,144,112</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>-145,901,785</t>
+          <t>-458,469,705</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
